--- a/Enzyme_Kinetics/reactionRate.xlsx
+++ b/Enzyme_Kinetics/reactionRate.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Minutes</t>
   </si>
   <si>
-    <t xml:space="preserve">Product</t>
+    <t xml:space="preserve">Substrate</t>
   </si>
 </sst>
 </file>
@@ -41,6 +41,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -62,6 +63,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -136,8 +138,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ122"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -146,13 +148,15 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="AMI1" s="0"/>
+      <c r="AMJ1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0</v>
+        <v>0.689</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -161,7 +165,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.178</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -170,7 +174,7 @@
         <v>0.2</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.269</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -179,7 +183,7 @@
         <v>0.3</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.336</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -188,7 +192,7 @@
         <v>0.4</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.376</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -197,7 +201,7 @@
         <v>0.5</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.412</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -206,7 +210,7 @@
         <v>0.6</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.429</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -215,7 +219,7 @@
         <v>0.7</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.462</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -224,7 +228,7 @@
         <v>0.8</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.488</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -233,7 +237,7 @@
         <v>0.9</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.51</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -242,7 +246,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.534</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -251,7 +255,7 @@
         <v>1.1</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.555</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -260,7 +264,7 @@
         <v>1.2</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.571</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -269,7 +273,7 @@
         <v>1.3</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.588</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -278,7 +282,7 @@
         <v>1.4</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -287,7 +291,7 @@
         <v>1.5</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.612</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -296,7 +300,7 @@
         <v>1.6</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.626</v>
+        <v>0.0629999999999999</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -305,7 +309,7 @@
         <v>1.7</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.634</v>
+        <v>0.0549999999999999</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -314,7 +318,7 @@
         <v>1.8</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.64</v>
+        <v>0.0489999999999999</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -323,7 +327,7 @@
         <v>1.9</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0.646</v>
+        <v>0.0429999999999999</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -332,7 +336,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.651</v>
+        <v>0.0379999999999999</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -341,7 +345,7 @@
         <v>2.1</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.657</v>
+        <v>0.0319999999999999</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -350,7 +354,7 @@
         <v>2.2</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.658</v>
+        <v>0.0309999999999999</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -359,7 +363,7 @@
         <v>2.3</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.664</v>
+        <v>0.0249999999999999</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -368,7 +372,7 @@
         <v>2.4</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>0.666</v>
+        <v>0.0229999999999999</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -377,7 +381,7 @@
         <v>2.5</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.671</v>
+        <v>0.0179999999999999</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -386,7 +390,7 @@
         <v>2.6</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.669</v>
+        <v>0.0199999999999999</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -395,7 +399,7 @@
         <v>2.7</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>0.662</v>
+        <v>0.0269999999999999</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -404,7 +408,7 @@
         <v>2.8</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>0.674</v>
+        <v>0.0149999999999999</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -413,7 +417,7 @@
         <v>2.9</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.675</v>
+        <v>0.0139999999999999</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,7 +426,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.675</v>
+        <v>0.0139999999999999</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,7 +435,7 @@
         <v>3.1</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>0.679</v>
+        <v>0.0099999999999999</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -440,7 +444,7 @@
         <v>3.2</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>0.68</v>
+        <v>0.0089999999999999</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -449,7 +453,7 @@
         <v>3.3</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>0.68</v>
+        <v>0.0089999999999999</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -458,7 +462,7 @@
         <v>3.4</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -467,7 +471,7 @@
         <v>3.5</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>0.684</v>
+        <v>0.00499999999999989</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -476,7 +480,7 @@
         <v>3.6</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>0.682</v>
+        <v>0.0069999999999999</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -485,7 +489,7 @@
         <v>3.7</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>0.684</v>
+        <v>0.00499999999999989</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -494,7 +498,7 @@
         <v>3.8</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>0.683</v>
+        <v>0.00599999999999989</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -503,7 +507,7 @@
         <v>3.9</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -512,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>0.682</v>
+        <v>0.0069999999999999</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -521,7 +525,7 @@
         <v>4.1</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -530,7 +534,7 @@
         <v>4.2</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -539,7 +543,7 @@
         <v>4.3</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>0.686</v>
+        <v>0.00299999999999989</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -548,7 +552,7 @@
         <v>4.4</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -557,7 +561,7 @@
         <v>4.5</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -566,7 +570,7 @@
         <v>4.6</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>0.686</v>
+        <v>0.00299999999999989</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -575,7 +579,7 @@
         <v>4.7</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -584,7 +588,7 @@
         <v>4.8</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -593,7 +597,7 @@
         <v>4.9</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -602,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -611,7 +615,7 @@
         <v>5.1</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,7 +624,7 @@
         <v>5.2</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -629,7 +633,7 @@
         <v>5.3</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -638,7 +642,7 @@
         <v>5.4</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -647,7 +651,7 @@
         <v>5.5</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -656,7 +660,7 @@
         <v>5.6</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -665,7 +669,7 @@
         <v>5.7</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -674,7 +678,7 @@
         <v>5.8</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -683,7 +687,7 @@
         <v>5.9</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -692,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -701,7 +705,7 @@
         <v>6.09999999999999</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -710,7 +714,7 @@
         <v>6.19999999999999</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,7 +723,7 @@
         <v>6.29999999999999</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -728,7 +732,7 @@
         <v>6.39999999999999</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -737,7 +741,7 @@
         <v>6.49999999999999</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -746,7 +750,7 @@
         <v>6.59999999999999</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -755,7 +759,7 @@
         <v>6.69999999999999</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -764,7 +768,7 @@
         <v>6.79999999999999</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -773,7 +777,7 @@
         <v>6.89999999999999</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -782,7 +786,7 @@
         <v>6.99999999999999</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,7 +795,7 @@
         <v>7.09999999999999</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -800,7 +804,7 @@
         <v>7.19999999999999</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -809,7 +813,7 @@
         <v>7.29999999999999</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -818,7 +822,7 @@
         <v>7.39999999999999</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -827,7 +831,7 @@
         <v>7.49999999999999</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -836,7 +840,7 @@
         <v>7.59999999999999</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -845,7 +849,7 @@
         <v>7.69999999999999</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -854,7 +858,7 @@
         <v>7.79999999999999</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -863,7 +867,7 @@
         <v>7.89999999999999</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -872,7 +876,7 @@
         <v>7.99999999999999</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -881,7 +885,7 @@
         <v>8.09999999999999</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -890,7 +894,7 @@
         <v>8.19999999999999</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -899,7 +903,7 @@
         <v>8.29999999999999</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -908,7 +912,7 @@
         <v>8.39999999999999</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -917,7 +921,7 @@
         <v>8.49999999999999</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -926,7 +930,7 @@
         <v>8.59999999999999</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -935,7 +939,7 @@
         <v>8.69999999999999</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -944,7 +948,7 @@
         <v>8.79999999999999</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -953,7 +957,7 @@
         <v>8.89999999999998</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -962,7 +966,7 @@
         <v>8.99999999999998</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -971,7 +975,7 @@
         <v>9.09999999999998</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -980,7 +984,7 @@
         <v>9.19999999999998</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -989,7 +993,7 @@
         <v>9.29999999999998</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -998,7 +1002,7 @@
         <v>9.39999999999998</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1007,7 +1011,7 @@
         <v>9.49999999999998</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1016,7 +1020,7 @@
         <v>9.59999999999998</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1025,7 +1029,7 @@
         <v>9.69999999999998</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1034,7 +1038,7 @@
         <v>9.79999999999998</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>0.685</v>
+        <v>0.00399999999999989</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1043,7 +1047,7 @@
         <v>9.89999999999998</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>0.692</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1052,7 +1056,7 @@
         <v>9.99999999999998</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1061,7 +1065,7 @@
         <v>10.1</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,7 +1074,7 @@
         <v>10.2</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1079,7 +1083,7 @@
         <v>10.3</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1088,7 +1092,7 @@
         <v>10.4</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1097,7 +1101,7 @@
         <v>10.5</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1106,7 +1110,7 @@
         <v>10.6</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1115,7 +1119,7 @@
         <v>10.7</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1124,7 +1128,7 @@
         <v>10.8</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1133,7 +1137,7 @@
         <v>10.9</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1142,7 +1146,7 @@
         <v>11</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>0.692</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1151,7 +1155,7 @@
         <v>11.1</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1160,7 +1164,7 @@
         <v>11.2</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>0.688</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1169,7 +1173,7 @@
         <v>11.3</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1178,7 +1182,7 @@
         <v>11.4</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1187,7 +1191,7 @@
         <v>11.5</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>0.69</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1196,7 +1200,7 @@
         <v>11.6</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>0.691</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1205,7 +1209,7 @@
         <v>11.7</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>0.691</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,7 +1218,7 @@
         <v>11.8</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1223,7 +1227,7 @@
         <v>11.9</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>0.687</v>
+        <v>0.00199999999999989</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1232,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>0.689</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
